--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -638,22 +638,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -770,22 +770,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45869.45833333334</v>
+        <v>45869.5</v>
       </c>
     </row>
     <row r="4">
@@ -897,7 +897,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>45869.45833333334</v>
+        <v>45869.5</v>
       </c>
     </row>
     <row r="5">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45869.45833333334</v>
+        <v>45869.5</v>
       </c>
     </row>
     <row r="6">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>45869.45833333334</v>
+        <v>45869.5</v>
       </c>
     </row>
     <row r="7">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45869.89930555555</v>
+        <v>45869.79166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1689,129 +1689,261 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL10" s="3" t="n">
+        <v>45869.89930555555</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Whitecaps II</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Sporting KC II</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AL11" s="3" t="n">
         <v>45869.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL11"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45869.79166666666</v>
+        <v>45869.89930555555</v>
       </c>
     </row>
     <row r="10">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1812,138 +1812,6 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45869.89930555555</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45869</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sporting KC II</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
         <v>45869.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -166,21 +166,21 @@
     <t>Mash'al</t>
   </si>
   <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -193,19 +193,19 @@
     <t>Pakhtakor</t>
   </si>
   <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
     <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
   </si>
   <si>
     <t>New York RB II</t>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -166,21 +166,21 @@
     <t>Mash'al</t>
   </si>
   <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
     <t>Al Salt</t>
   </si>
   <si>
     <t>Al Hussein</t>
   </si>
   <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -193,19 +193,19 @@
     <t>Pakhtakor</t>
   </si>
   <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
     <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
   </si>
   <si>
     <t>New York RB II</t>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -166,21 +166,21 @@
     <t>Mash'al</t>
   </si>
   <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
   </si>
   <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>Al Salt</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -193,19 +193,19 @@
     <t>Pakhtakor</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
     <t>Al Jazeera</t>
   </si>
   <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
   </si>
   <si>
     <t>New York RB II</t>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -166,18 +166,18 @@
     <t>Mash'al</t>
   </si>
   <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
     <t>Al Hussein</t>
   </si>
   <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
     <t>Al Salt</t>
   </si>
   <si>
@@ -193,16 +193,16 @@
     <t>Pakhtakor</t>
   </si>
   <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
   </si>
   <si>
     <t>Shabab Al Ordon</t>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -166,21 +166,21 @@
     <t>Mash'al</t>
   </si>
   <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
   </si>
   <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -193,19 +193,19 @@
     <t>Pakhtakor</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
     <t>Al Jazeera</t>
   </si>
   <si>
     <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
   </si>
   <si>
     <t>New York RB II</t>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -1550,13 +1550,13 @@
         <v>67</v>
       </c>
       <c r="L9">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="M9">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="O9">
         <v>0</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
   <si>
     <t>Date</t>
   </si>
@@ -130,12 +130,12 @@
     <t>DateTime</t>
   </si>
   <si>
-    <t>11:00</t>
-  </si>
-  <si>
     <t>12:00</t>
   </si>
   <si>
+    <t>14:45</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -145,9 +145,6 @@
     <t>22:00</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
@@ -157,30 +154,18 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>2025/2026</t>
+  </si>
+  <si>
     <t>2025</t>
   </si>
   <si>
-    <t>2025/2026</t>
-  </si>
-  <si>
-    <t>Mash'al</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
     <t>Al Salt</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>Columbus Crew II</t>
   </si>
   <si>
@@ -190,22 +175,10 @@
     <t>Whitecaps II</t>
   </si>
   <si>
-    <t>Pakhtakor</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Sama Al Sarhan</t>
   </si>
   <si>
     <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
   </si>
   <si>
     <t>New York RB II</t>
@@ -584,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -714,29 +687,29 @@
         <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>58</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>67</v>
-      </c>
       <c r="L2">
         <v>0</v>
       </c>
@@ -810,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AK2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AL2" s="3">
-        <v>45869.45833333334</v>
+        <v>45869.5</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -827,112 +800,112 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>59</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>68</v>
-      </c>
       <c r="AK3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AL3" s="3">
-        <v>45869.5</v>
+        <v>45869.61458333334</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -940,19 +913,19 @@
         <v>45869</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
         <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -967,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1042,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AK4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AL4" s="3">
-        <v>45869.5</v>
+        <v>45869.79166666666</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1056,19 +1029,19 @@
         <v>45869</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1083,16 +1056,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1128,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -1158,13 +1131,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AK5" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AL5" s="3">
-        <v>45869.5</v>
+        <v>45869.89930555555</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1172,19 +1145,19 @@
         <v>45869</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1199,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1274,476 +1247,12 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AK6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AL6" s="3">
-        <v>45869.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38">
-      <c r="A7" s="2">
-        <v>45869</v>
-      </c>
-      <c r="B7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL7" s="3">
-        <v>45869.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38">
-      <c r="A8" s="2">
-        <v>45869</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL8" s="3">
-        <v>45869.79166666666</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38">
-      <c r="A9" s="2">
-        <v>45869</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L9">
-        <v>2.42</v>
-      </c>
-      <c r="M9">
-        <v>2.6</v>
-      </c>
-      <c r="N9">
-        <v>3.11</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>1.57</v>
-      </c>
-      <c r="AA9">
-        <v>2.15</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL9" s="3">
-        <v>45869.89930555555</v>
-      </c>
-    </row>
-    <row r="10" spans="1:38">
-      <c r="A10" s="2">
-        <v>45869</v>
-      </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL10" s="3">
         <v>45869.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -1068,37 +1068,37 @@
         <v>3.11</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z5">
         <v>1.57</v>
@@ -1107,28 +1107,28 @@
         <v>2.15</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ5" t="s">
         <v>59</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1091,49 +1091,49 @@
         <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y5" t="n">
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AA5" t="n">
         <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AC5" t="n">
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="n">
         <v>12</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1088,10 +1088,10 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
         <v>4</v>
@@ -1100,31 +1100,31 @@
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>1.06</v>
@@ -1136,7 +1136,7 @@
         <v>1.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>1.03</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3.26</v>
+        <v>3.11</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1088,58 +1088,58 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
         <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y5" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="M2" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
         <v>3.25</v>
@@ -695,7 +695,7 @@
         <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
         <v>3.8</v>
@@ -707,31 +707,31 @@
         <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB2" t="n">
         <v>2.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AD2" t="n">
         <v>5.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
         <v>2.25</v>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>4.46</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.62</v>
@@ -824,7 +824,7 @@
         <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
         <v>2.25</v>
@@ -836,28 +836,28 @@
         <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="Z3" t="n">
         <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD3" t="n">
         <v>4.75</v>
@@ -866,16 +866,16 @@
         <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,40 +938,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -980,34 +980,34 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1091,7 +1091,7 @@
         <v>1.7</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
         <v>4.15</v>
@@ -1100,34 +1100,34 @@
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
         <v>2.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD5" t="n">
         <v>6.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
         <v>2.43</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1220,22 +1220,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1244,34 +1244,34 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
@@ -1001,7 +1001,7 @@
         <v>1.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="AH4" t="n">
         <v>3</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1</v>
+        <v>5.35</v>
       </c>
       <c r="N6" t="n">
-        <v>5.98</v>
+        <v>6.45</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1229,13 +1229,13 @@
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1247,10 +1247,10 @@
         <v>1.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC6" t="n">
         <v>2.7</v>
@@ -1259,7 +1259,7 @@
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
         <v>1.6</v>
@@ -1268,10 +1268,10 @@
         <v>2.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1088,22 +1088,22 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
         <v>2.05</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1.11</v>
@@ -1112,19 +1112,19 @@
         <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
         <v>2.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1.07</v>
@@ -1133,7 +1133,7 @@
         <v>2.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
         <v>15.5</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -670,17 +670,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>5.33</v>
       </c>
       <c r="O2" t="n">
         <v>1.91</v>
@@ -692,62 +692,62 @@
         <v>2.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
         <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AI2" t="n">
         <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84', '90+1']</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
         <v>1.62</v>
@@ -824,58 +824,58 @@
         <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>11.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
@@ -956,16 +956,16 @@
         <v>1.67</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
         <v>3.8</v>
@@ -983,31 +983,31 @@
         <v>1.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
@@ -1088,10 +1088,10 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
         <v>4.25</v>
@@ -1100,46 +1100,46 @@
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y5" t="n">
         <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD5" t="n">
         <v>6.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="N6" t="n">
-        <v>6.45</v>
+        <v>6.14</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1220,19 +1220,19 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
         <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U6" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W6" t="n">
         <v>1.2</v>
@@ -1250,25 +1250,25 @@
         <v>5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
         <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AI6" t="n">
         <v>1.3</v>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -921,30 +921,30 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
         <v>2.1</v>
@@ -962,13 +962,13 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
         <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
         <v>1.2</v>
@@ -983,40 +983,40 @@
         <v>1.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AH4" t="n">
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '47']</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="N6" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1223,19 +1223,19 @@
         <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
         <v>3.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1247,31 +1247,31 @@
         <v>1.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AH6" t="n">
         <v>3.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>

--- a/jogos_2025-07-31.xlsx
+++ b/jogos_2025-07-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -683,13 +678,13 @@
         <v>5.33</v>
       </c>
       <c r="O2" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.75</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
         <v>1.47</v>
@@ -704,58 +699,55 @@
         <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.5</v>
+        <v>2.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['84', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>8.6</v>
+        <v>1.98</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>['84', '90+1']</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45869.5</v>
       </c>
     </row>
@@ -815,13 +807,13 @@
         <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>6.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
@@ -836,58 +828,55 @@
         <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>2.66</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.5</v>
+        <v>2.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.34</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="AI3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45869.61458333334</v>
       </c>
     </row>
@@ -947,13 +936,13 @@
         <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -968,58 +957,55 @@
         <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>2.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>1.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.33</v>
+        <v>2.79</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['9', '47']</t>
+        </is>
       </c>
       <c r="AG4" t="n">
-        <v>2.79</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>['9', '47']</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45869.79166666666</v>
       </c>
     </row>
@@ -1053,105 +1039,102 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3.78</v>
       </c>
       <c r="P5" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
         <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="U5" t="n">
         <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>1.17</v>
+        <v>2.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.3</v>
+        <v>3.04</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>6.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.32</v>
+        <v>2.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['14', '45+2']</t>
+        </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>12</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45869.89930555555</v>
       </c>
     </row>
@@ -1185,20 +1168,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1211,13 +1194,13 @@
         <v>6.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.2</v>
@@ -1232,58 +1215,55 @@
         <v>1.85</v>
       </c>
       <c r="V6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['7', '41']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['59', '64', '73']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AJ6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45869.91666666666</v>
       </c>
     </row>
